--- a/res/vuz/urfu.xlsx
+++ b/res/vuz/urfu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8F7514-F234-4358-B1D1-C51A35466650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843C3BEF-2267-4630-8EBC-6EC34A40DB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="505">
   <si>
     <t>#name</t>
   </si>
@@ -1544,7 +1544,10 @@
     <t>167</t>
   </si>
   <si>
-    <t>+01.03.01 +01.03.03 + 01.03.04 +02.03.01 +02.03.03 +03.03.01 +03.03.02 +08.03.01 +08.05.01 +09.03.01 +09.03.02 +09.03.03 +09.03.04 +10.03.01 +10.05.01 +10.05.02 +10.05.04 +11.03.01 +11.03.02 +11.03.03 +11.03.04 +12.03.01 +13.03.01 +13.03.02 +13.03.03 +14.03.02 +14.05.01 +14.05.02 +14.05.04 +17.05.01 +27.03.01 +27.03.02 +27.03.03 +27.03.04 +27.03.05 +27.05.01 +28.03.02</t>
+    <t>+01.03.01 +01.03.03 +01.03.04 +02.03.01 +02.03.03 +03.03.01 +03.03.02 +08.03.01 +08.05.01 +09.03.01 +09.03.02 +09.03.03 +09.03.04 +10.03.01 +10.05.01 +10.05.02 +10.05.04 +11.03.01 +11.03.02 +11.03.03 +11.03.04 +12.03.01 +13.03.01 +13.03.02 +13.03.03 +14.03.02 +14.05.01 +14.05.02 +14.05.04 +17.05.01 +27.03.01 +27.03.02 +27.03.03 +27.03.04 +27.03.05 +27.05.01 +28.03.02</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -4667,6 +4670,9 @@
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>504</v>
+      </c>
       <c r="B170" s="3" t="s">
         <v>49</v>
       </c>
@@ -4681,6 +4687,9 @@
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B171" s="3" t="s">
         <v>47</v>
       </c>
@@ -4695,6 +4704,9 @@
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="B172" s="3" t="s">
         <v>50</v>
       </c>
@@ -4709,6 +4721,9 @@
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="B173" s="3" t="s">
         <v>50</v>
       </c>
@@ -4723,6 +4738,9 @@
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B174" s="3" t="s">
         <v>50</v>
       </c>
@@ -4737,6 +4755,9 @@
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B175" s="3" t="s">
         <v>50</v>
       </c>
@@ -4751,6 +4772,9 @@
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="B176" s="3" t="s">
         <v>54</v>
       </c>
